--- a/Parcial 3/Riesgo de Credito.xlsx
+++ b/Parcial 3/Riesgo de Credito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\OneDrive\Desktop\TRABAJO\UNI\8VO SEMESTRE\ADMINISTRACION_RIESGOS\Parcial 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE93C4A-FFFA-4683-BE51-6C69AA1C7E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4666483C-988E-4B7D-BCF5-E15E56F6F61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9C803BB7-A573-4C3E-A51D-ED2F10C94F32}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9C803BB7-A573-4C3E-A51D-ED2F10C94F32}"/>
   </bookViews>
   <sheets>
     <sheet name="E1" sheetId="1" r:id="rId1"/>
@@ -799,12 +799,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09FCC15C-7963-44B0-918E-68F101E1D07D}">
   <dimension ref="B25:K30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="12.109375" customWidth="1"/>
+    <col min="2" max="3" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="25" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
         <v>0</v>
       </c>
@@ -818,7 +818,7 @@
       </c>
       <c r="I25" s="5"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>1</v>
       </c>
@@ -842,7 +842,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>2</v>
       </c>
@@ -862,7 +862,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>3</v>
       </c>
@@ -882,7 +882,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>4</v>
       </c>
@@ -914,15 +914,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B50160A-9ACA-4974-808D-5661D8AD107B}">
   <dimension ref="B24:L38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="24" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
         <v>0</v>
       </c>
@@ -936,7 +936,7 @@
       </c>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="8" t="s">
         <v>1</v>
       </c>
@@ -957,7 +957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="8" t="s">
         <v>2</v>
       </c>
@@ -977,7 +977,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="8" t="s">
         <v>3</v>
       </c>
@@ -997,7 +997,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="12" t="s">
         <v>4</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>7.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="8" t="s">
         <v>8</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="8" t="s">
         <v>9</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="12" t="s">
         <v>15</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>6.7599999999999993E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="8" t="s">
         <v>10</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="8" t="s">
         <v>11</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="8" t="s">
         <v>12</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="36" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="12" t="s">
         <v>13</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>2.1599999999999998E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="15" t="s">
         <v>14</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="F38" t="s">
         <v>17</v>
       </c>
